--- a/tame_output/ON/bt/strategyON_20231223.xlsx
+++ b/tame_output/ON/bt/strategyON_20231223.xlsx
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537933</v>
+        <v>3.095206606537932</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597769</v>
+        <v>3.147410092597768</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527689</v>
+        <v>3.120684616527688</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844648</v>
+        <v>3.118866618844647</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373824</v>
+        <v>3.123416866373823</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502552</v>
+        <v>3.141819250502551</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728035</v>
+        <v>3.146730118728034</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487813</v>
+        <v>3.146053372487812</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823384</v>
+        <v>3.146265744823383</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524824</v>
+        <v>3.157777201524823</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068704</v>
+        <v>3.157294380068703</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714846</v>
+        <v>3.147014107714845</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097102</v>
+        <v>3.163432091097101</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762262</v>
+        <v>3.169279212762261</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583695</v>
+        <v>3.199276732583694</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742725</v>
+        <v>3.238767863742724</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589525</v>
+        <v>3.260068416589524</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872958</v>
+        <v>3.306739876872957</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.31216459594633</v>
+        <v>3.312164595946329</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43048,7 +43048,7 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>3.31844982914334</v>
+        <v>3.318449829143339</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308504</v>
+        <v>3.311781349308503</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257517</v>
+        <v>3.271427670257516</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,7 +43117,7 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.252962387441541</v>
+        <v>3.25296238744154</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
@@ -43140,7 +43140,7 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.241257540662169</v>
+        <v>3.241257540662168</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
@@ -43163,7 +43163,7 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543325</v>
+        <v>3.285495323543324</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
@@ -43186,7 +43186,7 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.287726162978609</v>
+        <v>3.287726162978608</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
@@ -43209,7 +43209,7 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.275586179621268</v>
+        <v>3.275586179621267</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
@@ -43232,7 +43232,7 @@
         <v>45276</v>
       </c>
       <c r="B1814" t="n">
-        <v>3.268822948291749</v>
+        <v>3.268822948291748</v>
       </c>
       <c r="C1814" t="n">
         <v>3.123696569025415</v>
@@ -43255,7 +43255,7 @@
         <v>45277</v>
       </c>
       <c r="B1815" t="n">
-        <v>3.249478190992881</v>
+        <v>3.24947819099288</v>
       </c>
       <c r="C1815" t="n">
         <v>3.109676345532145</v>
@@ -43278,7 +43278,7 @@
         <v>45278</v>
       </c>
       <c r="B1816" t="n">
-        <v>3.291576855321624</v>
+        <v>3.291576855321623</v>
       </c>
       <c r="C1816" t="n">
         <v>3.127125924287274</v>
@@ -43301,7 +43301,7 @@
         <v>45279</v>
       </c>
       <c r="B1817" t="n">
-        <v>3.289048749923557</v>
+        <v>3.289048749923556</v>
       </c>
       <c r="C1817" t="n">
         <v>3.126153974671351</v>
@@ -43324,7 +43324,7 @@
         <v>45280</v>
       </c>
       <c r="B1818" t="n">
-        <v>3.308072195160701</v>
+        <v>3.3080721951607</v>
       </c>
       <c r="C1818" t="n">
         <v>3.115456695754193</v>
@@ -43347,7 +43347,7 @@
         <v>45281</v>
       </c>
       <c r="B1819" t="n">
-        <v>3.318993081823467</v>
+        <v>3.318993081823466</v>
       </c>
       <c r="C1819" t="n">
         <v>3.125373651216407</v>
@@ -43370,22 +43370,22 @@
         <v>45282</v>
       </c>
       <c r="B1820" t="n">
-        <v>3.159375987083914</v>
+        <v>3.159375987083913</v>
       </c>
       <c r="C1820" t="n">
         <v>3.132226628875955</v>
       </c>
       <c r="D1820" t="n">
-        <v>0.2774784611357053</v>
+        <v>0.2775223361203537</v>
       </c>
       <c r="E1820" t="n">
-        <v>3.24286158901649</v>
+        <v>3.242879139010349</v>
       </c>
       <c r="F1820" t="n">
-        <v>1.923296803938465</v>
+        <v>1.923340678923113</v>
       </c>
       <c r="G1820" t="n">
-        <v>4.286204711239035</v>
+        <v>4.286231036229824</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231223.xlsx
+++ b/tame_output/ON/bt/strategyON_20231223.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>91.0%</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -934,12 +934,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -954,11 +954,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.5%</t>
+          <t>339.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-160.6%</t>
+          <t>-160.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-114.7%</t>
+          <t>-115.0%</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-18.3%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1260,11 +1260,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1283,27 +1283,27 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-139.3%</t>
+          <t>-133.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.2%</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>117.7%</t>
+          <t>117.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1413,11 +1413,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>112.9%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -42479,16 +42479,16 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-3.318130959076608</v>
+        <v>-3.385976429627905</v>
       </c>
       <c r="E1781" t="n">
-        <v>1.739512509529609</v>
+        <v>1.71237432130909</v>
       </c>
       <c r="F1781" t="n">
-        <v>0.3031499977753486</v>
+        <v>0.2353045272240518</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.24901131613921</v>
+        <v>3.208304033808432</v>
       </c>
     </row>
     <row r="1782">
@@ -42502,16 +42502,16 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-3.313147208404699</v>
+        <v>-3.380992678955996</v>
       </c>
       <c r="E1782" t="n">
-        <v>1.753344590389284</v>
+        <v>1.726206402168766</v>
       </c>
       <c r="F1782" t="n">
-        <v>0.3081337484472573</v>
+        <v>0.2402882778959605</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.263840147133267</v>
+        <v>3.223132864802489</v>
       </c>
     </row>
     <row r="1783">
@@ -42525,16 +42525,16 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-3.306761069455144</v>
+        <v>-3.37460654000644</v>
       </c>
       <c r="E1783" t="n">
-        <v>1.762627248980895</v>
+        <v>1.735489060760377</v>
       </c>
       <c r="F1783" t="n">
-        <v>0.3081337484472573</v>
+        <v>0.2402882778959605</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.270568350145056</v>
+        <v>3.229861067814278</v>
       </c>
     </row>
     <row r="1784">
@@ -42548,16 +42548,16 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-3.318566419773776</v>
+        <v>-3.386411890325073</v>
       </c>
       <c r="E1784" t="n">
-        <v>1.761921197612985</v>
+        <v>1.734783009392466</v>
       </c>
       <c r="F1784" t="n">
-        <v>0.2963283981286247</v>
+        <v>0.2284829275773279</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.267501228713419</v>
+        <v>3.22679394638264</v>
       </c>
     </row>
     <row r="1785">
@@ -42571,16 +42571,16 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-3.30983460899511</v>
+        <v>-3.377680079546407</v>
       </c>
       <c r="E1785" t="n">
-        <v>1.771361379534341</v>
+        <v>1.744223191313822</v>
       </c>
       <c r="F1785" t="n">
-        <v>0.3050602089072909</v>
+        <v>0.2372147383559942</v>
       </c>
       <c r="G1785" t="n">
-        <v>3.278687772790508</v>
+        <v>3.23798049045973</v>
       </c>
     </row>
     <row r="1786">
@@ -42594,16 +42594,16 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-3.303497722350658</v>
+        <v>-3.371343192901954</v>
       </c>
       <c r="E1786" t="n">
-        <v>1.769206953140107</v>
+        <v>1.742068764919588</v>
       </c>
       <c r="F1786" t="n">
-        <v>0.3050602089072909</v>
+        <v>0.2372147383559942</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.273998591738493</v>
+        <v>3.233291309407715</v>
       </c>
     </row>
     <row r="1787">
@@ -42617,16 +42617,16 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-3.300963274623289</v>
+        <v>-3.368808745174586</v>
       </c>
       <c r="E1787" t="n">
-        <v>1.780183390033248</v>
+        <v>1.753045201812729</v>
       </c>
       <c r="F1787" t="n">
-        <v>0.3050602089072909</v>
+        <v>0.2372147383559942</v>
       </c>
       <c r="G1787" t="n">
-        <v>3.283961249540687</v>
+        <v>3.243253967209909</v>
       </c>
     </row>
     <row r="1788">
@@ -42640,16 +42640,16 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-3.301039173603894</v>
+        <v>-3.368884644155191</v>
       </c>
       <c r="E1788" t="n">
-        <v>1.772567710633916</v>
+        <v>1.745429522413397</v>
       </c>
       <c r="F1788" t="n">
-        <v>0.3058234695966178</v>
+        <v>0.237977999045321</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.276833886147193</v>
+        <v>3.236126603816415</v>
       </c>
     </row>
     <row r="1789">
@@ -42663,16 +42663,16 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-3.31154136316324</v>
+        <v>-3.379386833714537</v>
       </c>
       <c r="E1789" t="n">
-        <v>1.746131410600551</v>
+        <v>1.718993222380032</v>
       </c>
       <c r="F1789" t="n">
-        <v>0.2953212800372711</v>
+        <v>0.2274758094859744</v>
       </c>
       <c r="G1789" t="n">
-        <v>3.248297148201958</v>
+        <v>3.20758986587118</v>
       </c>
     </row>
     <row r="1790">
@@ -42686,16 +42686,16 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-3.313374625842357</v>
+        <v>-3.381220096393653</v>
       </c>
       <c r="E1790" t="n">
-        <v>1.746098945375026</v>
+        <v>1.718960757154507</v>
       </c>
       <c r="F1790" t="n">
-        <v>0.2953212800372711</v>
+        <v>0.2274758094859744</v>
       </c>
       <c r="G1790" t="n">
-        <v>3.248997988048079</v>
+        <v>3.208290705717302</v>
       </c>
     </row>
     <row r="1791">
@@ -42709,16 +42709,16 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-3.318383740903941</v>
+        <v>-3.386229211455237</v>
       </c>
       <c r="E1791" t="n">
-        <v>1.744612379179252</v>
+        <v>1.717474190958733</v>
       </c>
       <c r="F1791" t="n">
-        <v>0.2943267024787364</v>
+        <v>0.2264812319274397</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.248918321341818</v>
+        <v>3.20821103901104</v>
       </c>
     </row>
     <row r="1792">
@@ -42732,16 +42732,16 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-3.322089297540755</v>
+        <v>-3.389934768092052</v>
       </c>
       <c r="E1792" t="n">
-        <v>1.742357881764891</v>
+        <v>1.715219693544372</v>
       </c>
       <c r="F1792" t="n">
-        <v>0.2924570272211015</v>
+        <v>0.2246115566698048</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.247024241427603</v>
+        <v>3.206316959096825</v>
       </c>
     </row>
     <row r="1793">
@@ -42755,16 +42755,16 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-3.32085697218339</v>
+        <v>-3.388702442734687</v>
       </c>
       <c r="E1793" t="n">
-        <v>1.743270663970157</v>
+        <v>1.716132475749638</v>
       </c>
       <c r="F1793" t="n">
-        <v>0.2930874035931391</v>
+        <v>0.2252419330418423</v>
       </c>
       <c r="G1793" t="n">
-        <v>3.247822319313145</v>
+        <v>3.207115036982366</v>
       </c>
     </row>
     <row r="1794">
@@ -42778,16 +42778,16 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-3.310528975167538</v>
+        <v>-3.378374445718834</v>
       </c>
       <c r="E1794" t="n">
-        <v>1.751531770940711</v>
+        <v>1.724393582720192</v>
       </c>
       <c r="F1794" t="n">
-        <v>0.3034154006089912</v>
+        <v>0.2355699300576945</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.258149025686869</v>
+        <v>3.217441743356091</v>
       </c>
     </row>
     <row r="1795">
@@ -42801,16 +42801,16 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-3.310412640019982</v>
+        <v>-3.378258110571279</v>
       </c>
       <c r="E1795" t="n">
-        <v>1.75809896520157</v>
+        <v>1.730960776981051</v>
       </c>
       <c r="F1795" t="n">
-        <v>0.303531735756547</v>
+        <v>0.2356862652052502</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.264739486977239</v>
+        <v>3.224032204646461</v>
       </c>
     </row>
     <row r="1796">
@@ -42824,16 +42824,16 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-3.312258049596849</v>
+        <v>-3.380103520148146</v>
       </c>
       <c r="E1796" t="n">
-        <v>1.754334771816211</v>
+        <v>1.727196583595693</v>
       </c>
       <c r="F1796" t="n">
-        <v>0.303531735756547</v>
+        <v>0.2356862652052502</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.261713457422628</v>
+        <v>3.221006175091849</v>
       </c>
     </row>
     <row r="1797">
@@ -42847,16 +42847,16 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-3.31075961707175</v>
+        <v>-3.378605087623047</v>
       </c>
       <c r="E1797" t="n">
-        <v>1.754872432687384</v>
+        <v>1.727734244466866</v>
       </c>
       <c r="F1797" t="n">
-        <v>0.3050301682816459</v>
+        <v>0.2371846977303491</v>
       </c>
       <c r="G1797" t="n">
-        <v>3.262550804798821</v>
+        <v>3.221843522468042</v>
       </c>
     </row>
     <row r="1798">
@@ -42870,16 +42870,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-3.318823869264484</v>
+        <v>-3.386669339815781</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.752924709753602</v>
+        <v>1.725786521533084</v>
       </c>
       <c r="F1798" t="n">
-        <v>0.296965916088912</v>
+        <v>0.2291204455376153</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.258990231426492</v>
+        <v>3.218282949095714</v>
       </c>
     </row>
     <row r="1799">
@@ -42893,16 +42893,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-3.320153836725696</v>
+        <v>-3.387999307276993</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.752392722769118</v>
+        <v>1.725254534548599</v>
       </c>
       <c r="F1799" t="n">
-        <v>0.296965916088912</v>
+        <v>0.2291204455376153</v>
       </c>
       <c r="G1799" t="n">
-        <v>3.258990231426492</v>
+        <v>3.218282949095714</v>
       </c>
     </row>
     <row r="1800">
@@ -42916,16 +42916,16 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-3.092289153992185</v>
+        <v>-3.160134624543482</v>
       </c>
       <c r="E1800" t="n">
-        <v>1.845755068969684</v>
+        <v>1.818616880749165</v>
       </c>
       <c r="F1800" t="n">
-        <v>0.296965916088912</v>
+        <v>0.2291204455376153</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.261206704533654</v>
+        <v>3.220499422202876</v>
       </c>
     </row>
     <row r="1801">
@@ -42939,16 +42939,16 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-2.844187590124968</v>
+        <v>-2.912033060676265</v>
       </c>
       <c r="E1801" t="n">
-        <v>1.952530290861663</v>
+        <v>1.925392102641144</v>
       </c>
       <c r="F1801" t="n">
-        <v>0.296965916088912</v>
+        <v>0.2291204455376153</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.268741300878746</v>
+        <v>3.228034018547968</v>
       </c>
     </row>
     <row r="1802">
@@ -42962,16 +42962,16 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-2.547349190731638</v>
+        <v>-2.615194661282935</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.072688661592453</v>
+        <v>2.045550473371934</v>
       </c>
       <c r="F1802" t="n">
-        <v>0.4118204045700397</v>
+        <v>0.343974934018743</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.33907700494088</v>
+        <v>3.298369722610102</v>
       </c>
     </row>
     <row r="1803">
@@ -42985,16 +42985,16 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-2.243709633906202</v>
+        <v>-2.311555104457498</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.195821558788314</v>
+        <v>2.168683370567795</v>
       </c>
       <c r="F1803" t="n">
-        <v>0.4118204045700397</v>
+        <v>0.343974934018743</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.340754079406567</v>
+        <v>3.300046797075789</v>
       </c>
     </row>
     <row r="1804">
@@ -43008,16 +43008,16 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-1.954689027465493</v>
+        <v>-2.02253449801679</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.307369222814055</v>
+        <v>2.280231034593536</v>
       </c>
       <c r="F1804" t="n">
-        <v>0.4118204045700397</v>
+        <v>0.343974934018743</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.336693500856024</v>
+        <v>3.295986218525246</v>
       </c>
     </row>
     <row r="1805">
@@ -43031,16 +43031,16 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-1.669969100201596</v>
+        <v>-1.737814570752893</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.426477333063631</v>
+        <v>2.399339144843113</v>
       </c>
       <c r="F1805" t="n">
-        <v>0.6965403318339369</v>
+        <v>0.6286948612826402</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.51274559655838</v>
+        <v>3.472038314227602</v>
       </c>
     </row>
     <row r="1806">
@@ -43054,16 +43054,16 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-1.386207430710056</v>
+        <v>-1.454052901261352</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.545294164034054</v>
+        <v>2.518155975813535</v>
       </c>
       <c r="F1806" t="n">
-        <v>0.6965403318339369</v>
+        <v>0.6286948612826402</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.518057759732187</v>
+        <v>3.477350477401409</v>
       </c>
     </row>
     <row r="1807">
@@ -43077,16 +43077,16 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-1.124559036317415</v>
+        <v>-1.192404506868712</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.643196109237744</v>
+        <v>2.616057921017225</v>
       </c>
       <c r="F1807" t="n">
-        <v>0.9581887262265776</v>
+        <v>0.8903432556752808</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.668289383814405</v>
+        <v>3.627582101483627</v>
       </c>
     </row>
     <row r="1808">
@@ -43100,16 +43100,16 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-0.8103925981780825</v>
+        <v>-0.8782380687293793</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.766326359509589</v>
+        <v>2.739188171289071</v>
       </c>
       <c r="F1808" t="n">
-        <v>1.27235516436591</v>
+        <v>1.204509693814613</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.854252921714117</v>
+        <v>3.813545639383339</v>
       </c>
     </row>
     <row r="1809">
@@ -43123,16 +43123,16 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>-0.6878808940723101</v>
+        <v>-0.7557263646236069</v>
       </c>
       <c r="E1809" t="n">
-        <v>2.833745424778638</v>
+        <v>2.806607236558119</v>
       </c>
       <c r="F1809" t="n">
-        <v>1.394866868471682</v>
+        <v>1.327021397920386</v>
       </c>
       <c r="G1809" t="n">
-        <v>3.94617432780432</v>
+        <v>3.905467045473542</v>
       </c>
     </row>
     <row r="1810">
@@ -43146,16 +43146,16 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>-0.5264923601455818</v>
+        <v>-0.5943378306968785</v>
       </c>
       <c r="E1810" t="n">
-        <v>2.908116962404808</v>
+        <v>2.880978774184289</v>
       </c>
       <c r="F1810" t="n">
-        <v>1.556255402398411</v>
+        <v>1.488409931847114</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.052823572215835</v>
+        <v>4.012116289885057</v>
       </c>
     </row>
     <row r="1811">
@@ -43169,16 +43169,16 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>-0.3467461689970756</v>
+        <v>-0.4145916395483723</v>
       </c>
       <c r="E1811" t="n">
-        <v>2.993543050916142</v>
+        <v>2.966404862695623</v>
       </c>
       <c r="F1811" t="n">
-        <v>1.556255402398411</v>
+        <v>1.488409931847114</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.066351184267767</v>
+        <v>4.025643901936989</v>
       </c>
     </row>
     <row r="1812">
@@ -43192,16 +43192,16 @@
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>-0.1879452425258527</v>
+        <v>-0.2557907130771494</v>
       </c>
       <c r="E1812" t="n">
-        <v>3.063650801755897</v>
+        <v>3.036512613535378</v>
       </c>
       <c r="F1812" t="n">
-        <v>1.556255402398411</v>
+        <v>1.488409931847114</v>
       </c>
       <c r="G1812" t="n">
-        <v>4.072938564519032</v>
+        <v>4.032231282188254</v>
       </c>
     </row>
     <row r="1813">
@@ -43215,16 +43215,16 @@
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>-0.0951567842204758</v>
+        <v>-0.1630022547717725</v>
       </c>
       <c r="E1813" t="n">
-        <v>3.089676933512754</v>
+        <v>3.062538745292235</v>
       </c>
       <c r="F1813" t="n">
-        <v>1.649043860703788</v>
+        <v>1.581198390152491</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.117522387936965</v>
+        <v>4.076815105606187</v>
       </c>
     </row>
     <row r="1814">
@@ -43238,16 +43238,16 @@
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>-0.001136288849633904</v>
+        <v>-0.06898175940093065</v>
       </c>
       <c r="E1814" t="n">
-        <v>3.122885629171815</v>
+        <v>3.095747440951296</v>
       </c>
       <c r="F1814" t="n">
-        <v>1.658886301196771</v>
+        <v>1.591040830645474</v>
       </c>
       <c r="G1814" t="n">
-        <v>4.11902834974348</v>
+        <v>4.078321067412701</v>
       </c>
     </row>
     <row r="1815">
@@ -43261,16 +43261,16 @@
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>0.08896667905688915</v>
+        <v>0.0211212085055924</v>
       </c>
       <c r="E1815" t="n">
-        <v>3.144906592841154</v>
+        <v>3.117768404620635</v>
       </c>
       <c r="F1815" t="n">
-        <v>1.661944495484557</v>
+        <v>1.59409902493326</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.106843042822881</v>
+        <v>4.066135760492103</v>
       </c>
     </row>
     <row r="1816">
@@ -43284,16 +43284,16 @@
         <v>3.127125924287274</v>
       </c>
       <c r="D1816" t="n">
-        <v>0.1330958497784643</v>
+        <v>0.06525037922716759</v>
       </c>
       <c r="E1816" t="n">
-        <v>3.180007839884913</v>
+        <v>3.152869651664394</v>
       </c>
       <c r="F1816" t="n">
-        <v>1.745963668471827</v>
+        <v>1.67811819792053</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.174704125370371</v>
+        <v>4.133996843039593</v>
       </c>
     </row>
     <row r="1817">
@@ -43307,16 +43307,16 @@
         <v>3.126153974671351</v>
       </c>
       <c r="D1817" t="n">
-        <v>0.1428658939561591</v>
+        <v>0.07502042340486237</v>
       </c>
       <c r="E1817" t="n">
-        <v>3.182943907940067</v>
+        <v>3.155805719719549</v>
       </c>
       <c r="F1817" t="n">
-        <v>1.825322559526893</v>
+        <v>1.757477088975596</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.221347510387488</v>
+        <v>4.18064022805671</v>
       </c>
     </row>
     <row r="1818">
@@ -43330,16 +43330,16 @@
         <v>3.115456695754193</v>
       </c>
       <c r="D1818" t="n">
-        <v>0.1795042167241338</v>
+        <v>0.1116587461728371</v>
       </c>
       <c r="E1818" t="n">
-        <v>3.1869019581301</v>
+        <v>3.159763769909581</v>
       </c>
       <c r="F1818" t="n">
-        <v>1.825322559526893</v>
+        <v>1.757477088975596</v>
       </c>
       <c r="G1818" t="n">
-        <v>4.210650231470331</v>
+        <v>4.169942949139553</v>
       </c>
     </row>
     <row r="1819">
@@ -43353,16 +43353,16 @@
         <v>3.125373651216407</v>
       </c>
       <c r="D1819" t="n">
-        <v>0.2281498951938671</v>
+        <v>0.1603044246425703</v>
       </c>
       <c r="E1819" t="n">
-        <v>3.216277184980207</v>
+        <v>3.189138996759688</v>
       </c>
       <c r="F1819" t="n">
-        <v>1.873968237996626</v>
+        <v>1.80612276744533</v>
       </c>
       <c r="G1819" t="n">
-        <v>4.249754594014385</v>
+        <v>4.209047311683607</v>
       </c>
     </row>
     <row r="1820">
@@ -43370,22 +43370,22 @@
         <v>45282</v>
       </c>
       <c r="B1820" t="n">
-        <v>3.159375987083913</v>
+        <v>3.145744527161811</v>
       </c>
       <c r="C1820" t="n">
         <v>3.132226628875955</v>
       </c>
       <c r="D1820" t="n">
-        <v>0.2775223361203537</v>
+        <v>0.2745306202680007</v>
       </c>
       <c r="E1820" t="n">
-        <v>3.242879139010349</v>
+        <v>3.241682452669408</v>
       </c>
       <c r="F1820" t="n">
-        <v>1.923340678923113</v>
+        <v>1.92034896307076</v>
       </c>
       <c r="G1820" t="n">
-        <v>4.286231036229824</v>
+        <v>4.284436006718413</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231223.xlsx
+++ b/tame_output/ON/bt/strategyON_20231223.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>339.5%</t>
+          <t>368.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-115.0%</t>
+          <t>-120.3%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-20.4%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-22.6%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>117.5%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>113.2%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537932</v>
+        <v>3.095206606537933</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597768</v>
+        <v>3.147410092597769</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527688</v>
+        <v>3.120684616527689</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844647</v>
+        <v>3.118866618844648</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373823</v>
+        <v>3.123416866373824</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502551</v>
+        <v>3.141819250502552</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728034</v>
+        <v>3.146730118728035</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487812</v>
+        <v>3.146053372487813</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823383</v>
+        <v>3.146265744823384</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524823</v>
+        <v>3.157777201524824</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068703</v>
+        <v>3.157294380068704</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714845</v>
+        <v>3.147014107714846</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097101</v>
+        <v>3.163432091097102</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762261</v>
+        <v>3.169279212762262</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583694</v>
+        <v>3.199276732583695</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742724</v>
+        <v>3.238767863742725</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589524</v>
+        <v>3.260068416589525</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872957</v>
+        <v>3.306739876872958</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946329</v>
+        <v>3.31216459594633</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43048,7 +43048,7 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>3.318449829143339</v>
+        <v>3.31844982914334</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308503</v>
+        <v>3.311781349308504</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257516</v>
+        <v>3.271427670257517</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,7 +43117,7 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.25296238744154</v>
+        <v>3.252962387441541</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
@@ -43140,7 +43140,7 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.241257540662168</v>
+        <v>3.241257540662169</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
@@ -43163,7 +43163,7 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543324</v>
+        <v>3.285495323543325</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
@@ -43186,7 +43186,7 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.287726162978608</v>
+        <v>3.287726162978609</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
@@ -43209,7 +43209,7 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.275586179621267</v>
+        <v>3.275586179621268</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
@@ -43232,7 +43232,7 @@
         <v>45276</v>
       </c>
       <c r="B1814" t="n">
-        <v>3.268822948291748</v>
+        <v>3.268822948291749</v>
       </c>
       <c r="C1814" t="n">
         <v>3.123696569025415</v>
@@ -43255,7 +43255,7 @@
         <v>45277</v>
       </c>
       <c r="B1815" t="n">
-        <v>3.24947819099288</v>
+        <v>3.249478190992881</v>
       </c>
       <c r="C1815" t="n">
         <v>3.109676345532145</v>
@@ -43278,7 +43278,7 @@
         <v>45278</v>
       </c>
       <c r="B1816" t="n">
-        <v>3.291576855321623</v>
+        <v>3.291576855321624</v>
       </c>
       <c r="C1816" t="n">
         <v>3.127125924287274</v>
@@ -43301,7 +43301,7 @@
         <v>45279</v>
       </c>
       <c r="B1817" t="n">
-        <v>3.289048749923556</v>
+        <v>3.289048749923557</v>
       </c>
       <c r="C1817" t="n">
         <v>3.126153974671351</v>
@@ -43324,7 +43324,7 @@
         <v>45280</v>
       </c>
       <c r="B1818" t="n">
-        <v>3.3080721951607</v>
+        <v>3.308072195160701</v>
       </c>
       <c r="C1818" t="n">
         <v>3.115456695754193</v>
@@ -43347,7 +43347,7 @@
         <v>45281</v>
       </c>
       <c r="B1819" t="n">
-        <v>3.318993081823466</v>
+        <v>3.318993081823467</v>
       </c>
       <c r="C1819" t="n">
         <v>3.125373651216407</v>
@@ -43370,22 +43370,22 @@
         <v>45282</v>
       </c>
       <c r="B1820" t="n">
-        <v>3.145744527161811</v>
+        <v>3.145744527161812</v>
       </c>
       <c r="C1820" t="n">
         <v>3.132226628875955</v>
       </c>
       <c r="D1820" t="n">
-        <v>0.2745306202680007</v>
+        <v>0.2207843270619727</v>
       </c>
       <c r="E1820" t="n">
-        <v>3.241682452669408</v>
+        <v>3.220183935386997</v>
       </c>
       <c r="F1820" t="n">
-        <v>1.92034896307076</v>
+        <v>1.866602669864732</v>
       </c>
       <c r="G1820" t="n">
-        <v>4.284436006718413</v>
+        <v>4.252188230794795</v>
       </c>
     </row>
   </sheetData>
